--- a/书单.xlsx
+++ b/书单.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\book_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1D301D-A2E3-457B-AA03-F0B0148C28C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18F4056-B610-4CFB-A4CB-BE86ABA83CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="300">
   <si>
     <t>书名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -35,10 +35,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -204,9 +200,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>三十六计(珍藏版)</t>
-  </si>
-  <si>
     <t>清华大学出版社（2018年6月）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -225,9 +218,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>非暴力沟通</t>
-  </si>
-  <si>
     <t>北京联合出版社（2018年8月）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -329,9 +319,6 @@
     <t>科学出版社</t>
   </si>
   <si>
-    <t>非理性繁荣</t>
-  </si>
-  <si>
     <t>罗伯特·J·希勒</t>
   </si>
   <si>
@@ -359,9 +346,6 @@
     <t>(美)科弗 等 著 阮吉寿,张华 译</t>
   </si>
   <si>
-    <t>图解密码技术</t>
-  </si>
-  <si>
     <t>结城浩</t>
   </si>
   <si>
@@ -386,9 +370,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>元认知 改变大脑的顽固思维</t>
-  </si>
-  <si>
     <t>大卫·迪绍夫</t>
   </si>
   <si>
@@ -552,9 +533,6 @@
   </si>
   <si>
     <t>上海人民出版社</t>
-  </si>
-  <si>
-    <t>科学革命的结构</t>
   </si>
   <si>
     <t>托马斯·库恩</t>
@@ -768,98 +746,432 @@
     <t>东方出版社</t>
   </si>
   <si>
+    <t>(英)霍布斯</t>
+  </si>
+  <si>
+    <t>商务印书馆</t>
+  </si>
+  <si>
+    <t>杀死一只知更鸟</t>
+  </si>
+  <si>
+    <t>(美) 哈珀·李</t>
+  </si>
+  <si>
+    <t>南海出版公司</t>
+  </si>
+  <si>
+    <t>呼啸山庄</t>
+  </si>
+  <si>
+    <t>(英) 艾米莉·勃朗特</t>
+  </si>
+  <si>
+    <t>译林出版社</t>
+  </si>
+  <si>
+    <t>第一性原理</t>
+  </si>
+  <si>
+    <t>中国商业出版社</t>
+  </si>
+  <si>
+    <t>马库斯·乔恩</t>
+  </si>
+  <si>
+    <t>皮亚杰认知和情感发展理论</t>
+  </si>
+  <si>
+    <t>巴里·J.沃兹沃思</t>
+  </si>
+  <si>
+    <t>华东师范大学出版社</t>
+  </si>
+  <si>
+    <t>逻辑哲学论</t>
+  </si>
+  <si>
+    <t>中国华侨出版社</t>
+  </si>
+  <si>
+    <t>(英) 路德维希·约瑟夫·约翰·维特根斯坦</t>
+  </si>
+  <si>
+    <t>犯罪心理学</t>
+  </si>
+  <si>
+    <t>(美) 柯特·R.巴托尔</t>
+  </si>
+  <si>
+    <t>经验主义与心灵哲学</t>
+  </si>
+  <si>
+    <t>复旦大学出版社</t>
+  </si>
+  <si>
+    <t>威尔弗里德·塞拉斯</t>
+  </si>
+  <si>
+    <t>Rich Dad Poor Dad（富爸爸穷爸爸）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plata Publishing</t>
+  </si>
+  <si>
+    <t>Kiyosaki, Robert T.</t>
+  </si>
+  <si>
+    <t>上海三联书店</t>
+  </si>
+  <si>
+    <t>中国青年出版社</t>
+  </si>
+  <si>
+    <t>(美) 史蒂芬·柯维</t>
+  </si>
+  <si>
+    <t>ISBN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787513335782</t>
+  </si>
+  <si>
+    <t>内容简介</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787508694672</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787520746144</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>利维坦</t>
-  </si>
-  <si>
-    <t>(英)霍布斯</t>
-  </si>
-  <si>
-    <t>商务印书馆</t>
-  </si>
-  <si>
-    <t>杀死一只知更鸟</t>
-  </si>
-  <si>
-    <t>(美) 哈珀·李</t>
-  </si>
-  <si>
-    <t>南海出版公司</t>
-  </si>
-  <si>
-    <t>呼啸山庄</t>
-  </si>
-  <si>
-    <t>(英) 艾米莉·勃朗特</t>
-  </si>
-  <si>
-    <t>译林出版社</t>
-  </si>
-  <si>
-    <t>第一性原理</t>
-  </si>
-  <si>
-    <t>中国商业出版社</t>
-  </si>
-  <si>
-    <t>马库斯·乔恩</t>
-  </si>
-  <si>
-    <t>皮亚杰认知和情感发展理论</t>
-  </si>
-  <si>
-    <t>巴里·J.沃兹沃思</t>
-  </si>
-  <si>
-    <t>华东师范大学出版社</t>
-  </si>
-  <si>
-    <t>逻辑哲学论</t>
-  </si>
-  <si>
-    <t>中国华侨出版社</t>
-  </si>
-  <si>
-    <t>(英) 路德维希·约瑟夫·约翰·维特根斯坦</t>
-  </si>
-  <si>
-    <t>犯罪心理学</t>
-  </si>
-  <si>
-    <t>(美) 柯特·R.巴托尔</t>
-  </si>
-  <si>
-    <t>经验主义与心灵哲学</t>
-  </si>
-  <si>
-    <t>复旦大学出版社</t>
-  </si>
-  <si>
-    <t>威尔弗里德·塞拉斯</t>
-  </si>
-  <si>
-    <t>Rich Dad Poor Dad（富爸爸穷爸爸）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Plata Publishing</t>
-  </si>
-  <si>
-    <t>Kiyosaki, Robert T.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787100123556</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787544766500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787520835374</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787544711630</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787576032093</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787511384096</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787115649775</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787309125764</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9780446611091</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>塔木德</t>
-  </si>
-  <si>
-    <t>上海三联书店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>高效能人士的七个习惯</t>
-  </si>
-  <si>
-    <t>中国青年出版社</t>
-  </si>
-  <si>
-    <t>(美) 史蒂芬·柯维</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787542651273</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787515360430</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9780393357820</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787506092098</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9780140444285</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787313100481</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787221173393</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787521762181</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787511244666</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787569534306</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787511732538</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787554613672</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787222078741</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787222079106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787518026371</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787115555632</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787511262981</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787514236866</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三十六计(珍藏版)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787302523659</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非暴力沟通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787551821636</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787522200514</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787559618740</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787521768527</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787802534483</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787111618775</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787513909884</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787111698159</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787508689012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非理性繁荣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787229176600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787516833452</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787030530264</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787300225791</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787115331809</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787111748663</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图解密码技术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元认知 改变大脑的顽固思维</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787115424914</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787518421831</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787302348580</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787111480594</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787300249933</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787544181846</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787010191652</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787301312988</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787301312971</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787111143291</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787030636218</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787516218082</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787559454911</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787111555353</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787521736250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>科学革命的结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787205106744</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787571013653</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787513350068</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787512622456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787111577973</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787111175070</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787208066069</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787301330661</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787115566287</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787521743333</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787544294829</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787534998553</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787115520739</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9787508647357</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1198,18 +1510,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="53.875" customWidth="1"/>
     <col min="3" max="3" width="19.25" customWidth="1"/>
     <col min="4" max="4" width="26.125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.625" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1218,838 +1532,1066 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="G2" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="G4" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="G5" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G6" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>249</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
+      <c r="G27" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>261</v>
+      </c>
+      <c r="C31" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>268</v>
+      </c>
+      <c r="C34" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>269</v>
+      </c>
+      <c r="C37" t="s">
+        <v>102</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>112</v>
+      </c>
+      <c r="C42" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43" t="s">
+        <v>116</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>120</v>
+      </c>
+      <c r="C45" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" t="s">
+        <v>128</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>129</v>
+      </c>
+      <c r="C48" t="s">
+        <v>131</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>132</v>
+      </c>
+      <c r="C49" t="s">
+        <v>133</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
+        <v>135</v>
+      </c>
+      <c r="C50" t="s">
+        <v>136</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" t="s">
+        <v>139</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" t="s">
+        <v>142</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
+        <v>144</v>
+      </c>
+      <c r="C53" t="s">
+        <v>145</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
+        <v>147</v>
+      </c>
+      <c r="C54" t="s">
+        <v>148</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" t="s">
+        <v>151</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>285</v>
+      </c>
+      <c r="C56" t="s">
+        <v>153</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
+        <v>155</v>
+      </c>
+      <c r="C57" t="s">
+        <v>156</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
+        <v>158</v>
+      </c>
+      <c r="C58" t="s">
+        <v>160</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
+        <v>161</v>
+      </c>
+      <c r="C59" t="s">
+        <v>163</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B60" t="s">
+        <v>164</v>
+      </c>
+      <c r="C60" t="s">
+        <v>165</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
+        <v>167</v>
+      </c>
+      <c r="C61" t="s">
+        <v>168</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B62" t="s">
+        <v>170</v>
+      </c>
+      <c r="C62" t="s">
+        <v>171</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B65" t="s">
+        <v>177</v>
+      </c>
+      <c r="C65" t="s">
         <v>179</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D65" t="s">
+        <v>178</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B66" t="s">
+        <v>180</v>
+      </c>
+      <c r="C66" t="s">
         <v>181</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
+      <c r="D66" t="s">
         <v>182</v>
       </c>
-      <c r="C13" t="s">
+      <c r="G66" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
         <v>183</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="C67" t="s">
+        <v>184</v>
+      </c>
+      <c r="D67" t="s">
+        <v>185</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B68" t="s">
+        <v>219</v>
+      </c>
+      <c r="C68" t="s">
+        <v>186</v>
+      </c>
+      <c r="D68" t="s">
+        <v>187</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B69" t="s">
+        <v>188</v>
+      </c>
+      <c r="C69" t="s">
+        <v>189</v>
+      </c>
+      <c r="D69" t="s">
+        <v>190</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B70" t="s">
+        <v>191</v>
+      </c>
+      <c r="C70" t="s">
+        <v>192</v>
+      </c>
+      <c r="D70" t="s">
+        <v>193</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B71" t="s">
+        <v>194</v>
+      </c>
+      <c r="C71" t="s">
+        <v>196</v>
+      </c>
+      <c r="D71" t="s">
+        <v>195</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B72" t="s">
+        <v>197</v>
+      </c>
+      <c r="C72" t="s">
+        <v>198</v>
+      </c>
+      <c r="D72" t="s">
+        <v>199</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B73" t="s">
+        <v>200</v>
+      </c>
+      <c r="C73" t="s">
+        <v>202</v>
+      </c>
+      <c r="D73" t="s">
+        <v>201</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B74" t="s">
+        <v>203</v>
+      </c>
+      <c r="C74" t="s">
+        <v>204</v>
+      </c>
+      <c r="D74" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
-        <v>90</v>
-      </c>
-      <c r="C31" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" t="s">
-        <v>98</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" t="s">
-        <v>100</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" t="s">
-        <v>105</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" t="s">
-        <v>108</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>110</v>
-      </c>
-      <c r="C38" t="s">
-        <v>113</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
-        <v>111</v>
-      </c>
-      <c r="C39" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>112</v>
-      </c>
-      <c r="C40" t="s">
-        <v>115</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" t="s">
-        <v>120</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
-        <v>118</v>
-      </c>
-      <c r="C42" t="s">
-        <v>120</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
-        <v>121</v>
-      </c>
-      <c r="C43" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
-        <v>123</v>
-      </c>
-      <c r="C44" t="s">
-        <v>124</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
-        <v>126</v>
-      </c>
-      <c r="C45" t="s">
-        <v>127</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
-        <v>129</v>
-      </c>
-      <c r="C46" t="s">
-        <v>131</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
-        <v>132</v>
-      </c>
-      <c r="C47" t="s">
-        <v>134</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
-        <v>135</v>
-      </c>
-      <c r="C48" t="s">
-        <v>137</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B49" t="s">
-        <v>138</v>
-      </c>
-      <c r="C49" t="s">
-        <v>139</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B50" t="s">
-        <v>141</v>
-      </c>
-      <c r="C50" t="s">
-        <v>142</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B51" t="s">
-        <v>144</v>
-      </c>
-      <c r="C51" t="s">
-        <v>145</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B52" t="s">
-        <v>147</v>
-      </c>
-      <c r="C52" t="s">
-        <v>148</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B53" t="s">
-        <v>150</v>
-      </c>
-      <c r="C53" t="s">
-        <v>151</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B54" t="s">
-        <v>153</v>
-      </c>
-      <c r="C54" t="s">
-        <v>154</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
-        <v>156</v>
-      </c>
-      <c r="C55" t="s">
-        <v>157</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B56" t="s">
-        <v>159</v>
-      </c>
-      <c r="C56" t="s">
-        <v>160</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" t="s">
-        <v>163</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B58" t="s">
-        <v>165</v>
-      </c>
-      <c r="C58" t="s">
-        <v>167</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B59" t="s">
-        <v>168</v>
-      </c>
-      <c r="C59" t="s">
-        <v>170</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B60" t="s">
-        <v>171</v>
-      </c>
-      <c r="C60" t="s">
-        <v>172</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B61" t="s">
-        <v>174</v>
-      </c>
-      <c r="C61" t="s">
-        <v>175</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B62" t="s">
-        <v>177</v>
-      </c>
-      <c r="C62" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B65" t="s">
-        <v>184</v>
-      </c>
-      <c r="C65" t="s">
-        <v>186</v>
-      </c>
-      <c r="D65" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B66" t="s">
-        <v>187</v>
-      </c>
-      <c r="C66" t="s">
-        <v>188</v>
-      </c>
-      <c r="D66" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B67" t="s">
-        <v>190</v>
-      </c>
-      <c r="C67" t="s">
-        <v>191</v>
-      </c>
-      <c r="D67" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B68" t="s">
-        <v>193</v>
-      </c>
-      <c r="C68" t="s">
-        <v>194</v>
-      </c>
-      <c r="D68" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B69" t="s">
-        <v>196</v>
-      </c>
-      <c r="C69" t="s">
-        <v>197</v>
-      </c>
-      <c r="D69" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B70" t="s">
-        <v>199</v>
-      </c>
-      <c r="C70" t="s">
-        <v>200</v>
-      </c>
-      <c r="D70" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B71" t="s">
-        <v>202</v>
-      </c>
-      <c r="C71" t="s">
-        <v>204</v>
-      </c>
-      <c r="D71" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B72" t="s">
+      <c r="G74" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B75" t="s">
         <v>205</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C75" t="s">
+        <v>207</v>
+      </c>
+      <c r="D75" t="s">
         <v>206</v>
       </c>
-      <c r="D72" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B73" t="s">
+      <c r="G75" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B76" t="s">
         <v>208</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C76" t="s">
         <v>210</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D76" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B74" t="s">
+      <c r="G76" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B77" t="s">
+        <v>229</v>
+      </c>
+      <c r="D77" t="s">
         <v>211</v>
       </c>
-      <c r="C74" t="s">
+      <c r="G77" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B78" t="s">
+        <v>230</v>
+      </c>
+      <c r="C78" t="s">
+        <v>213</v>
+      </c>
+      <c r="D78" t="s">
         <v>212</v>
       </c>
-      <c r="D74" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B75" t="s">
-        <v>213</v>
-      </c>
-      <c r="C75" t="s">
-        <v>215</v>
-      </c>
-      <c r="D75" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B76" t="s">
-        <v>216</v>
-      </c>
-      <c r="C76" t="s">
-        <v>218</v>
-      </c>
-      <c r="D76" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B77" t="s">
-        <v>219</v>
-      </c>
-      <c r="D77" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B78" t="s">
-        <v>221</v>
-      </c>
-      <c r="C78" t="s">
-        <v>223</v>
-      </c>
-      <c r="D78" t="s">
-        <v>222</v>
+      <c r="G78" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
